--- a/Data/True_data/current_data/cash_flow_statement.xlsx
+++ b/Data/True_data/current_data/cash_flow_statement.xlsx
@@ -471,7 +471,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -491,7 +490,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>193.85</v>
+        <v>190.98</v>
       </c>
     </row>
     <row r="7">
@@ -501,7 +500,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>58.45</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +510,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>-12.72</v>
+        <v>28.54</v>
       </c>
     </row>
     <row r="9">
@@ -521,7 +520,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>239.58</v>
+        <v>259.92</v>
       </c>
     </row>
     <row r="10">
@@ -531,7 +530,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>-80.54000000000001</v>
+        <v>-65.93000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -541,7 +540,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>-80.54000000000001</v>
+        <v>-65.93000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -551,7 +550,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>106.66</v>
+        <v>-7.67</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +560,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>-23.01</v>
+        <v>-84.64</v>
       </c>
     </row>
     <row r="14">
@@ -571,7 +570,7 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>83.65000000000001</v>
+        <v>-92.31</v>
       </c>
     </row>
     <row r="15">
@@ -581,7 +580,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>242.69</v>
+        <v>101.68</v>
       </c>
     </row>
     <row r="16">
@@ -591,7 +590,7 @@
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>265.53</v>
+        <v>469.12</v>
       </c>
     </row>
     <row r="17">
@@ -601,7 +600,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>508.22</v>
+        <v>570.8</v>
       </c>
     </row>
   </sheetData>
